--- a/ShoppingList/ブックスキャナリスト.xlsx
+++ b/ShoppingList/ブックスキャナリスト.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
@@ -33,12 +33,6 @@
       <sz val="6"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF7A7A7A"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="游ゴシック"/>
       <family val="2"/>
       <color theme="10"/>
@@ -46,30 +40,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Yu Gothic"/>
       <charset val="128"/>
       <family val="3"/>
-      <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Yu Gothic"/>
       <charset val="128"/>
       <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="10"/>
-      <sz val="12"/>
+      <name val="Yu Gothic"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FF17365D"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="10"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="0017365D"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -82,18 +85,8 @@
       <name val="Yu Gothic"/>
       <color rgb="00000000"/>
     </font>
-    <font>
-      <name val="Yu Gothic"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Yu Gothic"/>
-      <b val="1"/>
-      <color rgb="0017365D"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -102,17 +95,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF3F8"/>
+        <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -163,75 +151,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8" hidden="0"/>
+    <cellStyle name="標準 2" xfId="2"/>
     <cellStyle name="Normal" xfId="3" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -612,955 +586,953 @@
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
     <col width="30" customWidth="1" style="1" min="2" max="2"/>
-    <col width="14" customWidth="1" style="1" min="3" max="3"/>
-    <col width="14" customWidth="1" style="1" min="4" max="5"/>
-    <col width="14" customWidth="1" style="1" min="5" max="5"/>
-    <col width="16" customWidth="1" style="1" min="6" max="7"/>
+    <col width="14" customWidth="1" style="1" min="3" max="5"/>
+    <col width="16" customWidth="1" style="1" min="6" max="6"/>
     <col width="14" customWidth="1" style="1" min="7" max="7"/>
     <col width="10" customWidth="1" style="1" min="8" max="8"/>
     <col width="14" customWidth="1" style="1" min="9" max="9"/>
     <col width="22" customWidth="1" style="1" min="10" max="10"/>
-    <col width="18" customWidth="1" style="1" min="11" max="13"/>
+    <col width="18" customWidth="1" style="1" min="11" max="11"/>
     <col width="24" customWidth="1" style="1" min="12" max="12"/>
     <col width="26" customWidth="1" style="1" min="13" max="13"/>
     <col width="55" customWidth="1" style="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="1">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>メーカー</t>
         </is>
       </c>
-      <c r="B1" s="19" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>型番</t>
         </is>
       </c>
-      <c r="C1" s="19" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>見開湾曲補正</t>
         </is>
       </c>
-      <c r="D1" s="19" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>指自動削除</t>
         </is>
       </c>
-      <c r="E1" s="19" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>自動位置補正</t>
         </is>
       </c>
-      <c r="F1" s="19" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>見開き自動分割</t>
         </is>
       </c>
-      <c r="G1" s="19" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>ピント調節</t>
         </is>
       </c>
-      <c r="H1" s="19" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>OCR</t>
         </is>
       </c>
-      <c r="I1" s="19" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>オートスキャン</t>
         </is>
       </c>
-      <c r="J1" s="19" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>ペダル</t>
         </is>
       </c>
-      <c r="K1" s="19" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>サイドライト</t>
         </is>
       </c>
-      <c r="L1" s="19" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>対応OS</t>
         </is>
       </c>
-      <c r="M1" s="19" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>湾曲補正方式</t>
         </is>
       </c>
-      <c r="N1" s="19" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" s="1">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>CZUR</t>
         </is>
       </c>
-      <c r="B2" s="21" t="n"/>
-      <c r="C2" s="21" t="n"/>
-      <c r="D2" s="21" t="n"/>
-      <c r="E2" s="21" t="n"/>
-      <c r="F2" s="21" t="n"/>
-      <c r="G2" s="21" t="n"/>
-      <c r="H2" s="21" t="n"/>
-      <c r="I2" s="21" t="n"/>
-      <c r="J2" s="21" t="n"/>
-      <c r="K2" s="21" t="n"/>
-      <c r="L2" s="21" t="n"/>
-      <c r="M2" s="21" t="n"/>
-      <c r="N2" s="21" t="n"/>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="12" t="n"/>
+      <c r="K2" s="12" t="n"/>
+      <c r="L2" s="12" t="n"/>
+      <c r="M2" s="12" t="n"/>
+      <c r="N2" s="12" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1" s="1">
-      <c r="A3" s="22" t="n"/>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="A3" s="13" t="n"/>
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>ET MAX</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D3" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E3" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F3" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>オート</t>
         </is>
       </c>
-      <c r="H3" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I3" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J3" s="22" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>フット/ハンド</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="L3" s="22" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t>Windows/Mac（要確認）</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t>物理レーザー計測+画像認識補正</t>
         </is>
       </c>
-      <c r="N3" s="22" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t>厚みのある本向けの上位候補。サイドライトとレーザー補正を重視する場合に比較対象。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" s="1">
-      <c r="A4" s="22" t="n"/>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="A4" s="13" t="n"/>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>ET24 Pro</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D4" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F4" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G4" s="22" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="H4" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I4" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J4" s="22" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>フット/ハンド</t>
         </is>
       </c>
-      <c r="K4" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="L4" s="22" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t>Windows/Mac/Linux</t>
         </is>
       </c>
-      <c r="M4" s="22" t="inlineStr">
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>物理レーザー計測+画像認識補正</t>
         </is>
       </c>
-      <c r="N4" s="22" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t>レーザー補正+サイドライト付きの安全候補。厚い本への強さを重視するなら最有力。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" s="1">
-      <c r="A5" s="22" t="n"/>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="A5" s="13" t="n"/>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Shine Ultra Pro</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E5" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F5" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>オート</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I5" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>フット</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr">
+      <c r="K5" s="13" t="inlineStr">
         <is>
           <t>なし/要確認</t>
         </is>
       </c>
-      <c r="L5" s="22" t="inlineStr">
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t>Windows/Mac要確認</t>
         </is>
       </c>
-      <c r="M5" s="22" t="inlineStr">
+      <c r="M5" s="13" t="inlineStr">
         <is>
           <t>画像認識（ソフト）補正</t>
         </is>
       </c>
-      <c r="N5" s="22" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>光沢紙では照明反射に注意。厚い本はET系/SV600と比較。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" s="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>iCODIS</t>
         </is>
       </c>
-      <c r="B6" s="21" t="n"/>
-      <c r="C6" s="21" t="n"/>
-      <c r="D6" s="21" t="n"/>
-      <c r="E6" s="21" t="n"/>
-      <c r="F6" s="21" t="n"/>
-      <c r="G6" s="21" t="n"/>
-      <c r="H6" s="21" t="n"/>
-      <c r="I6" s="21" t="n"/>
-      <c r="J6" s="21" t="n"/>
-      <c r="K6" s="21" t="n"/>
-      <c r="L6" s="21" t="n"/>
-      <c r="M6" s="21" t="n"/>
-      <c r="N6" s="21" t="n"/>
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
+      <c r="M6" s="12" t="n"/>
+      <c r="N6" s="12" t="n"/>
     </row>
     <row r="7" ht="48" customHeight="1" s="1">
-      <c r="A7" s="22" t="inlineStr"/>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="A7" s="13" t="n"/>
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Megascan PRO X7</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F7" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>オート</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I7" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>ハンド</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr">
+      <c r="K7" s="13" t="inlineStr">
         <is>
           <t>ECページ要確認</t>
         </is>
       </c>
-      <c r="L7" s="22" t="inlineStr">
+      <c r="L7" s="13" t="inlineStr">
         <is>
           <t>Windows/Mac要確認</t>
         </is>
       </c>
-      <c r="M7" s="22" t="inlineStr">
+      <c r="M7" s="13" t="inlineStr">
         <is>
           <t>画像認識（ソフト）補正</t>
         </is>
       </c>
-      <c r="N7" s="22" t="inlineStr">
+      <c r="N7" s="13" t="inlineStr">
         <is>
           <t>EC流通候補として復活。A3コスパ候補。厚い本はレーザー補正機より歪みが残る可能性あり。購入前にOS/ライト確認。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" s="1">
-      <c r="A8" s="22" t="inlineStr"/>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Megascan PRO X9</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>オート</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I8" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>ハンド</t>
         </is>
       </c>
-      <c r="K8" s="22" t="inlineStr">
+      <c r="K8" s="13" t="inlineStr">
         <is>
           <t>ECページ要確認</t>
         </is>
       </c>
-      <c r="L8" s="22" t="inlineStr">
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t>Windows/Mac要確認</t>
         </is>
       </c>
-      <c r="M8" s="22" t="inlineStr">
+      <c r="M8" s="13" t="inlineStr">
         <is>
           <t>画像認識（ソフト）補正</t>
         </is>
       </c>
-      <c r="N8" s="22" t="inlineStr">
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t>EC流通候補として復活。A3低予算候補。厚い本はレーザー補正機より歪みが残る可能性あり。購入前にOS/ライト確認。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1" s="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>iOCHOW</t>
         </is>
       </c>
-      <c r="B9" s="21" t="n"/>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="21" t="n"/>
-      <c r="F9" s="21" t="n"/>
-      <c r="G9" s="21" t="n"/>
-      <c r="H9" s="21" t="n"/>
-      <c r="I9" s="21" t="n"/>
-      <c r="J9" s="21" t="n"/>
-      <c r="K9" s="21" t="n"/>
-      <c r="L9" s="21" t="n"/>
-      <c r="M9" s="21" t="n"/>
-      <c r="N9" s="21" t="n"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="12" t="n"/>
     </row>
     <row r="10" ht="48" customHeight="1" s="1">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>？</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>オート</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I10" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J10" s="22" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>ハンド</t>
         </is>
       </c>
-      <c r="K10" s="22" t="inlineStr">
+      <c r="K10" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="L10" s="22" t="inlineStr">
+      <c r="L10" s="13" t="inlineStr">
         <is>
           <t>Windowsのみの可能性</t>
         </is>
       </c>
-      <c r="M10" s="22" t="inlineStr">
+      <c r="M10" s="13" t="inlineStr">
         <is>
           <t>ソフト補正推定</t>
         </is>
       </c>
-      <c r="N10" s="22" t="inlineStr">
+      <c r="N10" s="13" t="inlineStr">
         <is>
           <t>Mac非対応の指摘あり。Mac利用なら販売ページで要確認。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1" s="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Joyusing</t>
         </is>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="21" t="n"/>
-      <c r="G11" s="21" t="n"/>
-      <c r="H11" s="21" t="n"/>
-      <c r="I11" s="21" t="n"/>
-      <c r="J11" s="21" t="n"/>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="21" t="n"/>
-      <c r="M11" s="21" t="n"/>
-      <c r="N11" s="21" t="n"/>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="12" t="n"/>
+      <c r="N11" s="12" t="n"/>
     </row>
     <row r="12" ht="48" customHeight="1" s="1">
-      <c r="A12" s="22" t="inlineStr"/>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>V160 Pro</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I12" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>両方</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="13" t="inlineStr">
         <is>
           <t>ECページ要確認</t>
         </is>
       </c>
-      <c r="L12" s="22" t="inlineStr">
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t>Windows/Mac要確認</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="13" t="inlineStr">
         <is>
           <t>画像認識（ソフト）補正</t>
         </is>
       </c>
-      <c r="N12" s="22" t="inlineStr">
+      <c r="N12" s="13" t="inlineStr">
         <is>
           <t>EC流通候補として復活。書画カメラ寄りの業務用候補。厚い本の歪み補正はCZUR ET系/SV600より慎重に比較。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" s="1">
-      <c r="A13" s="22" t="inlineStr"/>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>V320 Pro</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I13" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>フット</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K13" s="13" t="inlineStr">
         <is>
           <t>ECページ要確認</t>
         </is>
       </c>
-      <c r="L13" s="22" t="inlineStr">
+      <c r="L13" s="13" t="inlineStr">
         <is>
           <t>Windows/Mac要確認</t>
         </is>
       </c>
-      <c r="M13" s="22" t="inlineStr">
+      <c r="M13" s="13" t="inlineStr">
         <is>
           <t>画像認識（ソフト）補正</t>
         </is>
       </c>
-      <c r="N13" s="22" t="inlineStr">
+      <c r="N13" s="13" t="inlineStr">
         <is>
           <t>EC流通候補として復活。高画素/業務用寄り候補。A3横・厚い本では実サンプル確認推奨。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1" s="1">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>サンワサプライ</t>
         </is>
       </c>
-      <c r="B14" s="21" t="n"/>
-      <c r="C14" s="21" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
-      <c r="F14" s="21" t="n"/>
-      <c r="G14" s="21" t="n"/>
-      <c r="H14" s="21" t="n"/>
-      <c r="I14" s="21" t="n"/>
-      <c r="J14" s="21" t="n"/>
-      <c r="K14" s="21" t="n"/>
-      <c r="L14" s="21" t="n"/>
-      <c r="M14" s="21" t="n"/>
-      <c r="N14" s="21" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="12" t="n"/>
+      <c r="N14" s="12" t="n"/>
     </row>
     <row r="15" ht="48" customHeight="1" s="1">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>400-CAM073</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>？</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>ハンド</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K15" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="L15" s="22" t="inlineStr">
+      <c r="L15" s="13" t="inlineStr">
         <is>
           <t>Windows/Mac要確認</t>
         </is>
       </c>
-      <c r="M15" s="22" t="inlineStr">
+      <c r="M15" s="13" t="inlineStr">
         <is>
           <t>画像認識（ソフト）補正</t>
         </is>
       </c>
-      <c r="N15" s="22" t="inlineStr">
+      <c r="N15" s="13" t="inlineStr">
         <is>
           <t>既存候補。光沢紙・Mac対応は購入前に確認。 対応OSは販売ページ/取扱説明書で購入前確認。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" s="1">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>400-CAM088 / EZ4-CAM088</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>〇/要確認</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>？</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>〇/要確認</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>〇/要確認</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>高さ調整</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>〇/要確認</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>〇/要確認</t>
         </is>
       </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="K16" s="22" t="inlineStr">
+      <c r="K16" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="L16" s="22" t="inlineStr">
+      <c r="L16" s="13" t="inlineStr">
         <is>
           <t>Windows/Mac要確認</t>
         </is>
       </c>
-      <c r="M16" s="22" t="inlineStr">
+      <c r="M16" s="13" t="inlineStr">
         <is>
           <t>画像認識（ソフト）補正</t>
         </is>
       </c>
-      <c r="N16" s="22" t="inlineStr">
+      <c r="N16" s="13" t="inlineStr">
         <is>
           <t>AI検索で追加提案。A2・2000万画素・アーム上下調整の候補として記録。公式ページ未確認のため要再確認。 対応OSは販売ページ/取扱説明書で購入前確認。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1" s="1">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Fujitsu（PFU）</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n"/>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="21" t="n"/>
-      <c r="K17" s="21" t="n"/>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="12" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1" s="1">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>ScanSnap SV600</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>なし（タイマー/ページめくり検出あり）</t>
         </is>
       </c>
-      <c r="K18" s="22" t="inlineStr">
+      <c r="K18" s="13" t="inlineStr">
         <is>
           <t>×（本体LED）</t>
         </is>
       </c>
-      <c r="L18" s="22" t="inlineStr">
+      <c r="L18" s="13" t="inlineStr">
         <is>
           <t>Windows 11/10、macOS 12以降</t>
         </is>
       </c>
-      <c r="M18" s="22" t="inlineStr">
+      <c r="M18" s="13" t="inlineStr">
         <is>
           <t>ラインセンサー+ブック補正</t>
         </is>
       </c>
-      <c r="N18" s="22" t="inlineStr">
+      <c r="N18" s="13" t="inlineStr">
         <is>
           <t>PFU公式でA3横、厚さ30mm、Windows/macOS対応、ページめくり検出・タイマー、ブック補正を確認。指はクリアエディター系の補正で削除/修正可能。</t>
         </is>
@@ -1593,13 +1565,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
     <col width="30" customWidth="1" style="1" min="2" max="2"/>
-    <col width="14" customWidth="1" style="1" min="3" max="3"/>
-    <col width="14" customWidth="1" style="1" min="4" max="4"/>
-    <col width="14" customWidth="1" style="1" min="5" max="5"/>
+    <col width="14" customWidth="1" style="1" min="3" max="5"/>
     <col width="16" customWidth="1" style="1" min="6" max="6"/>
     <col width="14" customWidth="1" style="1" min="7" max="7"/>
     <col width="10" customWidth="1" style="1" min="8" max="8"/>
@@ -1608,1063 +1578,1062 @@
     <col width="18" customWidth="1" style="1" min="11" max="11"/>
     <col width="24" customWidth="1" style="1" min="12" max="12"/>
     <col width="26" customWidth="1" style="1" min="13" max="13"/>
-    <col width="55" customWidth="1" style="1" min="14" max="14"/>
-    <col width="55" customWidth="1" style="1" min="15" max="15"/>
+    <col width="55" customWidth="1" style="1" min="14" max="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="1">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>メーカー</t>
         </is>
       </c>
-      <c r="B1" s="19" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>型番</t>
         </is>
       </c>
-      <c r="C1" s="19" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>見開湾曲補正</t>
         </is>
       </c>
-      <c r="D1" s="19" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>指自動削除</t>
         </is>
       </c>
-      <c r="E1" s="19" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>自動位置補正</t>
         </is>
       </c>
-      <c r="F1" s="19" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>見開き自動分割</t>
         </is>
       </c>
-      <c r="G1" s="19" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>ピント調節</t>
         </is>
       </c>
-      <c r="H1" s="19" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>OCR</t>
         </is>
       </c>
-      <c r="I1" s="19" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>オートスキャン</t>
         </is>
       </c>
-      <c r="J1" s="19" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>ペダル</t>
         </is>
       </c>
-      <c r="K1" s="19" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>サイドライト</t>
         </is>
       </c>
-      <c r="L1" s="19" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>対応OS</t>
         </is>
       </c>
-      <c r="M1" s="19" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>湾曲補正方式</t>
         </is>
       </c>
-      <c r="N1" s="19" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="O1" s="19" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>退避理由</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" s="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>CZUR</t>
         </is>
       </c>
-      <c r="B2" s="21" t="n"/>
-      <c r="C2" s="21" t="n"/>
-      <c r="D2" s="21" t="n"/>
-      <c r="E2" s="21" t="n"/>
-      <c r="F2" s="21" t="n"/>
-      <c r="G2" s="21" t="n"/>
-      <c r="H2" s="21" t="n"/>
-      <c r="I2" s="21" t="n"/>
-      <c r="J2" s="21" t="n"/>
-      <c r="K2" s="21" t="n"/>
-      <c r="L2" s="21" t="n"/>
-      <c r="M2" s="21" t="n"/>
-      <c r="N2" s="21" t="n"/>
-      <c r="O2" s="21" t="n"/>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="12" t="n"/>
+      <c r="K2" s="12" t="n"/>
+      <c r="L2" s="12" t="n"/>
+      <c r="M2" s="12" t="n"/>
+      <c r="N2" s="12" t="n"/>
+      <c r="O2" s="12" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1" s="1">
-      <c r="A3" s="22" t="n"/>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="A3" s="13" t="n"/>
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Aura S/Aura S Pro</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D3" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E3" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F3" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="H3" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I3" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J3" s="22" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>フット</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t>×/要確認</t>
         </is>
       </c>
-      <c r="L3" s="22" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t>Windows/Mac（要確認）</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t>ソフト補正</t>
         </is>
       </c>
-      <c r="N3" s="22" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t>低価格・省スペース寄り。厚い本はET系と比較。</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t>現行の有力候補としてはAura Mate Pro等に置き換わっている可能性が高く、2026年の推薦リストにも未掲載のため退避。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" s="1">
-      <c r="A4" s="22" t="n"/>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="A4" s="13" t="n"/>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Shine 800 A3 Pro</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F4" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G4" s="22" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>オート</t>
         </is>
       </c>
-      <c r="H4" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J4" s="22" t="inlineStr">
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>フット</t>
         </is>
       </c>
-      <c r="K4" s="22" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>×/要確認</t>
         </is>
       </c>
-      <c r="L4" s="22" t="inlineStr">
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t>Windows/Mac（要確認）</t>
         </is>
       </c>
-      <c r="M4" s="22" t="inlineStr">
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>ソフト補正</t>
         </is>
       </c>
-      <c r="N4" s="22" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t>A3対応だがブック用途の補正は弱めとして扱う。</t>
         </is>
       </c>
-      <c r="O4" s="22" t="inlineStr">
+      <c r="O4" s="13" t="inlineStr">
         <is>
           <t>現行CZUR候補として確認しづらく、ET系/Shine Ultra系より旧型・流通不明のため退避。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1" s="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>iCODIS</t>
         </is>
       </c>
-      <c r="B5" s="21" t="n"/>
-      <c r="C5" s="21" t="n"/>
-      <c r="D5" s="21" t="n"/>
-      <c r="E5" s="21" t="n"/>
-      <c r="F5" s="21" t="n"/>
-      <c r="G5" s="21" t="n"/>
-      <c r="H5" s="21" t="n"/>
-      <c r="I5" s="21" t="n"/>
-      <c r="J5" s="21" t="n"/>
-      <c r="K5" s="21" t="n"/>
-      <c r="L5" s="21" t="n"/>
-      <c r="M5" s="21" t="n"/>
-      <c r="N5" s="21" t="n"/>
-      <c r="O5" s="21" t="n"/>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="12" t="n"/>
+      <c r="M5" s="12" t="n"/>
+      <c r="N5" s="12" t="n"/>
+      <c r="O5" s="12" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1" s="1">
-      <c r="A6" s="22" t="n"/>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="A6" s="13" t="n"/>
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Megascan PRO X3</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>？</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E6" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>？</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>オート</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I6" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>？</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="13" t="inlineStr">
         <is>
           <t>ソフト補正推定</t>
         </is>
       </c>
-      <c r="N6" s="22" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t>公式仕様で再確認したい候補。</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t>公式/国内販売ページを確認できず、現行入手性が不明のため退避。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1" s="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>iOCHOW</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="n"/>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="21" t="n"/>
-      <c r="H7" s="21" t="n"/>
-      <c r="I7" s="21" t="n"/>
-      <c r="J7" s="21" t="n"/>
-      <c r="K7" s="21" t="n"/>
-      <c r="L7" s="21" t="n"/>
-      <c r="M7" s="21" t="n"/>
-      <c r="N7" s="21" t="n"/>
-      <c r="O7" s="21" t="n"/>
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="12" t="n"/>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="12" t="n"/>
+      <c r="N7" s="12" t="n"/>
+      <c r="O7" s="12" t="n"/>
     </row>
     <row r="8" ht="48" customHeight="1" s="1">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>？</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>？</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>固定/オート</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I8" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>？</t>
         </is>
       </c>
-      <c r="K8" s="22" t="inlineStr">
+      <c r="K8" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="L8" s="22" t="inlineStr">
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t>Windows中心（Mac要確認）</t>
         </is>
       </c>
-      <c r="M8" s="22" t="inlineStr">
+      <c r="M8" s="13" t="inlineStr">
         <is>
           <t>ソフト補正推定</t>
         </is>
       </c>
-      <c r="N8" s="22" t="inlineStr">
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t>購入前にMac対応を必ず確認。</t>
         </is>
       </c>
-      <c r="O8" s="22" t="inlineStr">
+      <c r="O8" s="13" t="inlineStr">
         <is>
           <t>旧型の可能性が高く、S5等の比較候補より優先度が低いため退避。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" s="1">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>？</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>オート</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I9" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>ハンド</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="L9" s="22" t="inlineStr">
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t>Windows中心（Mac要確認）</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="13" t="inlineStr">
         <is>
           <t>ソフト補正推定</t>
         </is>
       </c>
-      <c r="N9" s="22" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>購入前にMac対応を必ず確認。</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="13" t="inlineStr">
         <is>
           <t>旧型の可能性が高く、S5等の比較候補より優先度が低いため退避。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1" s="1">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Joyusing</t>
         </is>
       </c>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
-      <c r="G10" s="21" t="n"/>
-      <c r="H10" s="21" t="n"/>
-      <c r="I10" s="21" t="n"/>
-      <c r="J10" s="21" t="n"/>
-      <c r="K10" s="21" t="n"/>
-      <c r="L10" s="21" t="n"/>
-      <c r="M10" s="21" t="n"/>
-      <c r="N10" s="21" t="n"/>
-      <c r="O10" s="21" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="12" t="n"/>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="12" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1" s="1">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>V160</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>両方</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr">
+      <c r="K11" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="L11" s="22" t="inlineStr">
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="M11" s="22" t="inlineStr">
+      <c r="M11" s="13" t="inlineStr">
         <is>
           <t>ソフト補正推定</t>
         </is>
       </c>
-      <c r="N11" s="22" t="inlineStr">
+      <c r="N11" s="13" t="inlineStr">
         <is>
           <t>教育・業務用寄り。国内販売条件を確認。</t>
         </is>
       </c>
-      <c r="O11" s="22" t="inlineStr">
+      <c r="O11" s="13" t="inlineStr">
         <is>
           <t>国内購入候補としての現行入手性を確認できず、ブックスキャナー用途より書画カメラ寄りのため退避。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" s="1">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>V180</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I12" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>追加</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="L12" s="22" t="inlineStr">
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="13" t="inlineStr">
         <is>
           <t>ソフト補正推定</t>
         </is>
       </c>
-      <c r="N12" s="22" t="inlineStr">
+      <c r="N12" s="13" t="inlineStr">
         <is>
           <t>教育・業務用寄り。国内販売条件を確認。</t>
         </is>
       </c>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="O12" s="13" t="inlineStr">
         <is>
           <t>国内購入候補としての現行入手性を確認できず、ブックスキャナー用途より書画カメラ寄りのため退避。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" s="1">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>L140</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I13" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>フット</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K13" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="L13" s="22" t="inlineStr">
+      <c r="L13" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="M13" s="22" t="inlineStr">
+      <c r="M13" s="13" t="inlineStr">
         <is>
           <t>ソフト補正推定</t>
         </is>
       </c>
-      <c r="N13" s="22" t="inlineStr">
+      <c r="N13" s="13" t="inlineStr">
         <is>
           <t>教育・業務用寄り。国内販売条件を確認。</t>
         </is>
       </c>
-      <c r="O13" s="22" t="inlineStr">
+      <c r="O13" s="13" t="inlineStr">
         <is>
           <t>国内購入候補としての現行入手性を確認できず、ブックスキャナー用途より書画カメラ寄りのため退避。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" s="1">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>L180</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I14" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t>フット</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr">
+      <c r="K14" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="L14" s="22" t="inlineStr">
+      <c r="L14" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="M14" s="22" t="inlineStr">
+      <c r="M14" s="13" t="inlineStr">
         <is>
           <t>ソフト補正推定</t>
         </is>
       </c>
-      <c r="N14" s="22" t="inlineStr">
+      <c r="N14" s="13" t="inlineStr">
         <is>
           <t>教育・業務用寄り。国内販売条件を確認。</t>
         </is>
       </c>
-      <c r="O14" s="22" t="inlineStr">
+      <c r="O14" s="13" t="inlineStr">
         <is>
           <t>国内購入候補としての現行入手性を確認できず、ブックスキャナー用途より書画カメラ寄りのため退避。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" s="1">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>V320</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>フット</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K15" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="L15" s="22" t="inlineStr">
+      <c r="L15" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="M15" s="22" t="inlineStr">
+      <c r="M15" s="13" t="inlineStr">
         <is>
           <t>ソフト補正推定</t>
         </is>
       </c>
-      <c r="N15" s="22" t="inlineStr">
+      <c r="N15" s="13" t="inlineStr">
         <is>
           <t>教育・業務用寄り。国内販売条件を確認。</t>
         </is>
       </c>
-      <c r="O15" s="22" t="inlineStr">
+      <c r="O15" s="13" t="inlineStr">
         <is>
           <t>国内購入候補としての現行入手性を確認できず、ブックスキャナー用途より書画カメラ寄りのため退避。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" s="1">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>V321 Plus</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I16" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J16" s="22" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>フット</t>
         </is>
       </c>
-      <c r="K16" s="22" t="inlineStr">
+      <c r="K16" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="L16" s="22" t="inlineStr">
+      <c r="L16" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="M16" s="22" t="inlineStr">
+      <c r="M16" s="13" t="inlineStr">
         <is>
           <t>ソフト補正推定</t>
         </is>
       </c>
-      <c r="N16" s="22" t="inlineStr">
+      <c r="N16" s="13" t="inlineStr">
         <is>
           <t>教育・業務用寄り。国内販売条件を確認。</t>
         </is>
       </c>
-      <c r="O16" s="22" t="inlineStr">
+      <c r="O16" s="13" t="inlineStr">
         <is>
           <t>国内購入候補としての現行入手性を確認できず、ブックスキャナー用途より書画カメラ寄りのため退避。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1" s="1">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n"/>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="21" t="n"/>
-      <c r="K17" s="21" t="n"/>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="21" t="n"/>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="12" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1" s="1">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>SCA800UP</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>？</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>ナシ</t>
         </is>
       </c>
-      <c r="K18" s="22" t="inlineStr">
+      <c r="K18" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="L18" s="22" t="inlineStr">
+      <c r="L18" s="13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="M18" s="22" t="inlineStr">
+      <c r="M18" s="13" t="inlineStr">
         <is>
           <t>ソフト補正推定</t>
         </is>
       </c>
-      <c r="N18" s="22" t="inlineStr">
+      <c r="N18" s="13" t="inlineStr">
         <is>
           <t>購入前に国内在庫・OS・照明条件を確認。</t>
         </is>
       </c>
-      <c r="O18" s="22" t="inlineStr">
+      <c r="O18" s="13" t="inlineStr">
         <is>
           <t>メーカー/国内販売ページを確認できず、現行入手性が不明のため退避。</t>
         </is>
@@ -2682,93 +2651,93 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
     <col width="20" customWidth="1" style="1" min="1" max="1"/>
     <col width="110" customWidth="1" style="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="1">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="1">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>更新日</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="1">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>今回の修正</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>退避基準を緩め、公式サイトだけでなくAmazon/楽天/Yahoo等のEC流通候補もメイン候補に戻す方針へ変更。</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="4" ht="18" customHeight="1" s="1">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>復活させた機種</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>iCODIS Megascan PRO X7 / X9、Joyusing V160 Pro / V320 Pro。</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="18" customHeight="1" s="1">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>EC流通品は販売者により仕様差があるため、対応OS・サイドライト・付属品は購入直前に商品ページで確認。</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="6" ht="18" customHeight="1" s="1">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>SV600修正</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>ペダルはなし。ただしタイマー/ページめくり検出あり。指削除は補正機能で削除/修正可能として〇へ修正。</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="7" ht="18" customHeight="1" s="1">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>リンク方針</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>ハイパーリンクはメーカー名セルだけ。製品名セルのリンク痕跡は削除。</t>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>ハイパーリンクはメーカー名セルだけ。公式トップよりも調べやすさを優先し、iCODIS/Joyusing/iOCHOWは対象機種のEC検索、サンワサプライは400-CAM系の直販検索、PFUはSV600公式ページ、CZURは製品一覧へリンク。</t>
         </is>
       </c>
     </row>
